--- a/manufacturing_forms/011_material_storage_condition_review_request_form--manufacturing_forms.xlsx
+++ b/manufacturing_forms/011_material_storage_condition_review_request_form--manufacturing_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1126,8 +1126,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'user'}</t>
+          <t>user</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'User'}</t>
+          <t>User</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1172,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'lab'}</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Lab'}</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1206,12 +1206,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1223,12 +1223,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'lab'}</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Lab'}</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1257,12 +1257,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1274,12 +1274,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'refrigerated'}</t>
+          <t>refrigerated</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Refrigerated'}</t>
+          <t>Refrigerated</t>
         </is>
       </c>
     </row>
@@ -1291,12 +1291,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'ambient'}</t>
+          <t>ambient</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Ambient'}</t>
+          <t>Ambient</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1308,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'freezer'}</t>
+          <t>freezer</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Freezer'}</t>
+          <t>Freezer</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1342,12 +1342,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1359,12 +1359,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1376,12 +1376,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1393,12 +1393,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'lab'}</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Lab'}</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'warehouse'}</t>
+          <t>warehouse</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'Warehouse'}</t>
+          <t>Warehouse</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'manufacturing'}</t>
+          <t>manufacturing</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'Manufacturing'}</t>
+          <t>Manufacturing</t>
         </is>
       </c>
     </row>
@@ -1478,12 +1478,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'not_started'}</t>
+          <t>not_started</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'Not Started'}</t>
+          <t>Not Started</t>
         </is>
       </c>
     </row>
@@ -1495,12 +1495,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'in_progress'}</t>
+          <t>in_progress</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'In Progress'}</t>
+          <t>In Progress</t>
         </is>
       </c>
     </row>
@@ -1512,12 +1512,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'completed'}</t>
+          <t>completed</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'Completed'}</t>
+          <t>Completed</t>
         </is>
       </c>
     </row>
